--- a/assets/Ecommerce_Allocation_Request.xlsx
+++ b/assets/Ecommerce_Allocation_Request.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBB7B77-BF0B-4896-8049-40EF4BFF3B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B34F7F-F136-4E08-B014-771E431FCA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" customWidth="1"/>
@@ -496,10 +496,10 @@
         <v>470</v>
       </c>
       <c r="B2" s="3">
-        <v>24874</v>
+        <v>3786</v>
       </c>
       <c r="C2" s="3">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -507,10 +507,10 @@
         <v>470</v>
       </c>
       <c r="B3" s="3">
-        <v>66663</v>
+        <v>3827</v>
       </c>
       <c r="C3" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -518,10 +518,10 @@
         <v>470</v>
       </c>
       <c r="B4" s="3">
-        <v>69380</v>
+        <v>3833</v>
       </c>
       <c r="C4" s="3">
-        <v>12</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -529,10 +529,10 @@
         <v>470</v>
       </c>
       <c r="B5" s="3">
-        <v>74359</v>
+        <v>53406</v>
       </c>
       <c r="C5" s="3">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -540,7 +540,7 @@
         <v>470</v>
       </c>
       <c r="B6" s="3">
-        <v>74532</v>
+        <v>53407</v>
       </c>
       <c r="C6" s="3">
         <v>12</v>
@@ -551,7 +551,7 @@
         <v>470</v>
       </c>
       <c r="B7" s="3">
-        <v>84802</v>
+        <v>53408</v>
       </c>
       <c r="C7" s="3">
         <v>12</v>
@@ -562,7 +562,7 @@
         <v>470</v>
       </c>
       <c r="B8" s="3">
-        <v>85743</v>
+        <v>53410</v>
       </c>
       <c r="C8" s="3">
         <v>12</v>
@@ -573,7 +573,7 @@
         <v>470</v>
       </c>
       <c r="B9" s="3">
-        <v>87345</v>
+        <v>58609</v>
       </c>
       <c r="C9" s="3">
         <v>12</v>
@@ -584,7 +584,7 @@
         <v>470</v>
       </c>
       <c r="B10" s="3">
-        <v>87419</v>
+        <v>60971</v>
       </c>
       <c r="C10" s="3">
         <v>12</v>
@@ -595,7 +595,7 @@
         <v>470</v>
       </c>
       <c r="B11" s="3">
-        <v>88810</v>
+        <v>65819</v>
       </c>
       <c r="C11" s="3">
         <v>12</v>
@@ -606,10 +606,10 @@
         <v>470</v>
       </c>
       <c r="B12" s="3">
-        <v>89341</v>
+        <v>68563</v>
       </c>
       <c r="C12" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -617,7 +617,7 @@
         <v>470</v>
       </c>
       <c r="B13" s="3">
-        <v>89952</v>
+        <v>74158</v>
       </c>
       <c r="C13" s="3">
         <v>12</v>
@@ -628,10 +628,10 @@
         <v>470</v>
       </c>
       <c r="B14" s="3">
-        <v>90793</v>
+        <v>74167</v>
       </c>
       <c r="C14" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -639,10 +639,10 @@
         <v>470</v>
       </c>
       <c r="B15" s="3">
-        <v>92742</v>
+        <v>74359</v>
       </c>
       <c r="C15" s="3">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -650,10 +650,10 @@
         <v>470</v>
       </c>
       <c r="B16" s="3">
-        <v>93307</v>
+        <v>74532</v>
       </c>
       <c r="C16" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -661,10 +661,10 @@
         <v>470</v>
       </c>
       <c r="B17" s="3">
-        <v>94593</v>
+        <v>81764</v>
       </c>
       <c r="C17" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -672,10 +672,10 @@
         <v>470</v>
       </c>
       <c r="B18" s="3">
-        <v>94594</v>
+        <v>82580</v>
       </c>
       <c r="C18" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -683,7 +683,7 @@
         <v>470</v>
       </c>
       <c r="B19" s="3">
-        <v>94916</v>
+        <v>82581</v>
       </c>
       <c r="C19" s="3">
         <v>24</v>
@@ -694,10 +694,10 @@
         <v>470</v>
       </c>
       <c r="B20" s="3">
-        <v>95667</v>
+        <v>83184</v>
       </c>
       <c r="C20" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -705,10 +705,10 @@
         <v>470</v>
       </c>
       <c r="B21" s="3">
-        <v>95731</v>
+        <v>83689</v>
       </c>
       <c r="C21" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -716,10 +716,10 @@
         <v>470</v>
       </c>
       <c r="B22" s="3">
-        <v>95732</v>
+        <v>84540</v>
       </c>
       <c r="C22" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -727,10 +727,10 @@
         <v>470</v>
       </c>
       <c r="B23" s="3">
-        <v>95816</v>
+        <v>87343</v>
       </c>
       <c r="C23" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -738,10 +738,10 @@
         <v>470</v>
       </c>
       <c r="B24" s="3">
-        <v>95817</v>
+        <v>87534</v>
       </c>
       <c r="C24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -749,10 +749,10 @@
         <v>470</v>
       </c>
       <c r="B25" s="3">
-        <v>96315</v>
+        <v>87939</v>
       </c>
       <c r="C25" s="3">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -760,10 +760,10 @@
         <v>470</v>
       </c>
       <c r="B26" s="3">
-        <v>96316</v>
+        <v>88269</v>
       </c>
       <c r="C26" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -771,10 +771,10 @@
         <v>470</v>
       </c>
       <c r="B27" s="3">
-        <v>96317</v>
+        <v>88350</v>
       </c>
       <c r="C27" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -782,10 +782,10 @@
         <v>470</v>
       </c>
       <c r="B28" s="3">
-        <v>96318</v>
+        <v>88360</v>
       </c>
       <c r="C28" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -793,10 +793,10 @@
         <v>470</v>
       </c>
       <c r="B29" s="3">
-        <v>96319</v>
+        <v>88609</v>
       </c>
       <c r="C29" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -804,7 +804,7 @@
         <v>470</v>
       </c>
       <c r="B30" s="3">
-        <v>96517</v>
+        <v>89339</v>
       </c>
       <c r="C30" s="3">
         <v>12</v>
@@ -815,10 +815,10 @@
         <v>470</v>
       </c>
       <c r="B31" s="3">
-        <v>97529</v>
+        <v>89340</v>
       </c>
       <c r="C31" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -826,7 +826,7 @@
         <v>470</v>
       </c>
       <c r="B32" s="3">
-        <v>97544</v>
+        <v>89341</v>
       </c>
       <c r="C32" s="3">
         <v>6</v>
@@ -837,10 +837,10 @@
         <v>470</v>
       </c>
       <c r="B33" s="3">
-        <v>97698</v>
+        <v>90925</v>
       </c>
       <c r="C33" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -848,7 +848,7 @@
         <v>470</v>
       </c>
       <c r="B34" s="3">
-        <v>98149</v>
+        <v>91047</v>
       </c>
       <c r="C34" s="3">
         <v>12</v>
@@ -859,7 +859,7 @@
         <v>470</v>
       </c>
       <c r="B35" s="3">
-        <v>98150</v>
+        <v>91732</v>
       </c>
       <c r="C35" s="3">
         <v>8</v>
@@ -870,10 +870,10 @@
         <v>470</v>
       </c>
       <c r="B36" s="3">
-        <v>98175</v>
+        <v>92589</v>
       </c>
       <c r="C36" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -881,7 +881,7 @@
         <v>470</v>
       </c>
       <c r="B37" s="3">
-        <v>98219</v>
+        <v>92591</v>
       </c>
       <c r="C37" s="3">
         <v>12</v>
@@ -892,10 +892,10 @@
         <v>470</v>
       </c>
       <c r="B38" s="3">
-        <v>98310</v>
+        <v>92742</v>
       </c>
       <c r="C38" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -903,10 +903,10 @@
         <v>470</v>
       </c>
       <c r="B39" s="3">
-        <v>98334</v>
+        <v>92747</v>
       </c>
       <c r="C39" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -914,10 +914,10 @@
         <v>470</v>
       </c>
       <c r="B40" s="3">
-        <v>98377</v>
+        <v>92811</v>
       </c>
       <c r="C40" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>470</v>
       </c>
       <c r="B41" s="3">
-        <v>98437</v>
+        <v>93036</v>
       </c>
       <c r="C41" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -936,7 +936,7 @@
         <v>470</v>
       </c>
       <c r="B42" s="3">
-        <v>98451</v>
+        <v>93057</v>
       </c>
       <c r="C42" s="3">
         <v>12</v>
@@ -947,9 +947,372 @@
         <v>470</v>
       </c>
       <c r="B43" s="3">
-        <v>98541</v>
+        <v>93286</v>
       </c>
       <c r="C43" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>470</v>
+      </c>
+      <c r="B44" s="3">
+        <v>94140</v>
+      </c>
+      <c r="C44" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>470</v>
+      </c>
+      <c r="B45" s="3">
+        <v>94172</v>
+      </c>
+      <c r="C45" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>470</v>
+      </c>
+      <c r="B46" s="3">
+        <v>94173</v>
+      </c>
+      <c r="C46" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>470</v>
+      </c>
+      <c r="B47" s="3">
+        <v>94394</v>
+      </c>
+      <c r="C47" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>470</v>
+      </c>
+      <c r="B48" s="3">
+        <v>94400</v>
+      </c>
+      <c r="C48" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>470</v>
+      </c>
+      <c r="B49" s="3">
+        <v>94404</v>
+      </c>
+      <c r="C49" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>470</v>
+      </c>
+      <c r="B50" s="3">
+        <v>95590</v>
+      </c>
+      <c r="C50" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>470</v>
+      </c>
+      <c r="B51" s="3">
+        <v>95591</v>
+      </c>
+      <c r="C51" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>470</v>
+      </c>
+      <c r="B52" s="3">
+        <v>95735</v>
+      </c>
+      <c r="C52" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>470</v>
+      </c>
+      <c r="B53" s="3">
+        <v>95765</v>
+      </c>
+      <c r="C53" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>470</v>
+      </c>
+      <c r="B54" s="3">
+        <v>95768</v>
+      </c>
+      <c r="C54" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>470</v>
+      </c>
+      <c r="B55" s="3">
+        <v>95781</v>
+      </c>
+      <c r="C55" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>470</v>
+      </c>
+      <c r="B56" s="3">
+        <v>95907</v>
+      </c>
+      <c r="C56" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>470</v>
+      </c>
+      <c r="B57" s="3">
+        <v>97116</v>
+      </c>
+      <c r="C57" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>470</v>
+      </c>
+      <c r="B58" s="3">
+        <v>97118</v>
+      </c>
+      <c r="C58" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>470</v>
+      </c>
+      <c r="B59" s="3">
+        <v>97131</v>
+      </c>
+      <c r="C59" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>470</v>
+      </c>
+      <c r="B60" s="3">
+        <v>97245</v>
+      </c>
+      <c r="C60" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>470</v>
+      </c>
+      <c r="B61" s="3">
+        <v>97665</v>
+      </c>
+      <c r="C61" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>470</v>
+      </c>
+      <c r="B62" s="3">
+        <v>98149</v>
+      </c>
+      <c r="C62" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>470</v>
+      </c>
+      <c r="B63" s="3">
+        <v>98151</v>
+      </c>
+      <c r="C63" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>470</v>
+      </c>
+      <c r="B64" s="3">
+        <v>98263</v>
+      </c>
+      <c r="C64" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>470</v>
+      </c>
+      <c r="B65" s="3">
+        <v>98289</v>
+      </c>
+      <c r="C65" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>470</v>
+      </c>
+      <c r="B66" s="3">
+        <v>98344</v>
+      </c>
+      <c r="C66" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>470</v>
+      </c>
+      <c r="B67" s="3">
+        <v>98347</v>
+      </c>
+      <c r="C67" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>470</v>
+      </c>
+      <c r="B68" s="3">
+        <v>98372</v>
+      </c>
+      <c r="C68" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>470</v>
+      </c>
+      <c r="B69" s="3">
+        <v>98377</v>
+      </c>
+      <c r="C69" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>470</v>
+      </c>
+      <c r="B70" s="3">
+        <v>98378</v>
+      </c>
+      <c r="C70" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>470</v>
+      </c>
+      <c r="B71" s="3">
+        <v>98437</v>
+      </c>
+      <c r="C71" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>470</v>
+      </c>
+      <c r="B72" s="3">
+        <v>98445</v>
+      </c>
+      <c r="C72" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>470</v>
+      </c>
+      <c r="B73" s="3">
+        <v>98471</v>
+      </c>
+      <c r="C73" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>470</v>
+      </c>
+      <c r="B74" s="3">
+        <v>98540</v>
+      </c>
+      <c r="C74" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>470</v>
+      </c>
+      <c r="B75" s="3">
+        <v>98626</v>
+      </c>
+      <c r="C75" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>470</v>
+      </c>
+      <c r="B76" s="3">
+        <v>98634</v>
+      </c>
+      <c r="C76" s="3">
         <v>12</v>
       </c>
     </row>

--- a/assets/Ecommerce_Allocation_Request.xlsx
+++ b/assets/Ecommerce_Allocation_Request.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B34F7F-F136-4E08-B014-771E431FCA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19805415-4AE4-4DE4-BF84-DC639E282AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" customWidth="1"/>
@@ -496,10 +496,10 @@
         <v>470</v>
       </c>
       <c r="B2" s="3">
-        <v>3786</v>
+        <v>7652</v>
       </c>
       <c r="C2" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -507,10 +507,10 @@
         <v>470</v>
       </c>
       <c r="B3" s="3">
-        <v>3827</v>
+        <v>53406</v>
       </c>
       <c r="C3" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -518,10 +518,10 @@
         <v>470</v>
       </c>
       <c r="B4" s="3">
-        <v>3833</v>
+        <v>53546</v>
       </c>
       <c r="C4" s="3">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -529,7 +529,7 @@
         <v>470</v>
       </c>
       <c r="B5" s="3">
-        <v>53406</v>
+        <v>58609</v>
       </c>
       <c r="C5" s="3">
         <v>12</v>
@@ -540,10 +540,10 @@
         <v>470</v>
       </c>
       <c r="B6" s="3">
-        <v>53407</v>
+        <v>70739</v>
       </c>
       <c r="C6" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -551,7 +551,7 @@
         <v>470</v>
       </c>
       <c r="B7" s="3">
-        <v>53408</v>
+        <v>80815</v>
       </c>
       <c r="C7" s="3">
         <v>12</v>
@@ -562,10 +562,10 @@
         <v>470</v>
       </c>
       <c r="B8" s="3">
-        <v>53410</v>
+        <v>82595</v>
       </c>
       <c r="C8" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -573,7 +573,7 @@
         <v>470</v>
       </c>
       <c r="B9" s="3">
-        <v>58609</v>
+        <v>84559</v>
       </c>
       <c r="C9" s="3">
         <v>12</v>
@@ -584,10 +584,10 @@
         <v>470</v>
       </c>
       <c r="B10" s="3">
-        <v>60971</v>
+        <v>87885</v>
       </c>
       <c r="C10" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -595,7 +595,7 @@
         <v>470</v>
       </c>
       <c r="B11" s="3">
-        <v>65819</v>
+        <v>88609</v>
       </c>
       <c r="C11" s="3">
         <v>12</v>
@@ -606,10 +606,10 @@
         <v>470</v>
       </c>
       <c r="B12" s="3">
-        <v>68563</v>
+        <v>88810</v>
       </c>
       <c r="C12" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -617,7 +617,7 @@
         <v>470</v>
       </c>
       <c r="B13" s="3">
-        <v>74158</v>
+        <v>89337</v>
       </c>
       <c r="C13" s="3">
         <v>12</v>
@@ -628,10 +628,10 @@
         <v>470</v>
       </c>
       <c r="B14" s="3">
-        <v>74167</v>
+        <v>89340</v>
       </c>
       <c r="C14" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -639,10 +639,10 @@
         <v>470</v>
       </c>
       <c r="B15" s="3">
-        <v>74359</v>
+        <v>89952</v>
       </c>
       <c r="C15" s="3">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -650,10 +650,10 @@
         <v>470</v>
       </c>
       <c r="B16" s="3">
-        <v>74532</v>
+        <v>92546</v>
       </c>
       <c r="C16" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -661,7 +661,7 @@
         <v>470</v>
       </c>
       <c r="B17" s="3">
-        <v>81764</v>
+        <v>93016</v>
       </c>
       <c r="C17" s="3">
         <v>6</v>
@@ -672,7 +672,7 @@
         <v>470</v>
       </c>
       <c r="B18" s="3">
-        <v>82580</v>
+        <v>93042</v>
       </c>
       <c r="C18" s="3">
         <v>24</v>
@@ -683,10 +683,10 @@
         <v>470</v>
       </c>
       <c r="B19" s="3">
-        <v>82581</v>
+        <v>95732</v>
       </c>
       <c r="C19" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -694,7 +694,7 @@
         <v>470</v>
       </c>
       <c r="B20" s="3">
-        <v>83184</v>
+        <v>95768</v>
       </c>
       <c r="C20" s="3">
         <v>6</v>
@@ -705,10 +705,10 @@
         <v>470</v>
       </c>
       <c r="B21" s="3">
-        <v>83689</v>
+        <v>96559</v>
       </c>
       <c r="C21" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -716,10 +716,10 @@
         <v>470</v>
       </c>
       <c r="B22" s="3">
-        <v>84540</v>
+        <v>97858</v>
       </c>
       <c r="C22" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -727,7 +727,7 @@
         <v>470</v>
       </c>
       <c r="B23" s="3">
-        <v>87343</v>
+        <v>97859</v>
       </c>
       <c r="C23" s="3">
         <v>8</v>
@@ -738,10 +738,10 @@
         <v>470</v>
       </c>
       <c r="B24" s="3">
-        <v>87534</v>
+        <v>97860</v>
       </c>
       <c r="C24" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -749,10 +749,10 @@
         <v>470</v>
       </c>
       <c r="B25" s="3">
-        <v>87939</v>
+        <v>97873</v>
       </c>
       <c r="C25" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -760,560 +760,10 @@
         <v>470</v>
       </c>
       <c r="B26" s="3">
-        <v>88269</v>
+        <v>97878</v>
       </c>
       <c r="C26" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
-        <v>470</v>
-      </c>
-      <c r="B27" s="3">
-        <v>88350</v>
-      </c>
-      <c r="C27" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>470</v>
-      </c>
-      <c r="B28" s="3">
-        <v>88360</v>
-      </c>
-      <c r="C28" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
-        <v>470</v>
-      </c>
-      <c r="B29" s="3">
-        <v>88609</v>
-      </c>
-      <c r="C29" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
-        <v>470</v>
-      </c>
-      <c r="B30" s="3">
-        <v>89339</v>
-      </c>
-      <c r="C30" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
-        <v>470</v>
-      </c>
-      <c r="B31" s="3">
-        <v>89340</v>
-      </c>
-      <c r="C31" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>470</v>
-      </c>
-      <c r="B32" s="3">
-        <v>89341</v>
-      </c>
-      <c r="C32" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>470</v>
-      </c>
-      <c r="B33" s="3">
-        <v>90925</v>
-      </c>
-      <c r="C33" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>470</v>
-      </c>
-      <c r="B34" s="3">
-        <v>91047</v>
-      </c>
-      <c r="C34" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
-        <v>470</v>
-      </c>
-      <c r="B35" s="3">
-        <v>91732</v>
-      </c>
-      <c r="C35" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>470</v>
-      </c>
-      <c r="B36" s="3">
-        <v>92589</v>
-      </c>
-      <c r="C36" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
-        <v>470</v>
-      </c>
-      <c r="B37" s="3">
-        <v>92591</v>
-      </c>
-      <c r="C37" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>470</v>
-      </c>
-      <c r="B38" s="3">
-        <v>92742</v>
-      </c>
-      <c r="C38" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
-        <v>470</v>
-      </c>
-      <c r="B39" s="3">
-        <v>92747</v>
-      </c>
-      <c r="C39" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
-        <v>470</v>
-      </c>
-      <c r="B40" s="3">
-        <v>92811</v>
-      </c>
-      <c r="C40" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
-        <v>470</v>
-      </c>
-      <c r="B41" s="3">
-        <v>93036</v>
-      </c>
-      <c r="C41" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
-        <v>470</v>
-      </c>
-      <c r="B42" s="3">
-        <v>93057</v>
-      </c>
-      <c r="C42" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>470</v>
-      </c>
-      <c r="B43" s="3">
-        <v>93286</v>
-      </c>
-      <c r="C43" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>470</v>
-      </c>
-      <c r="B44" s="3">
-        <v>94140</v>
-      </c>
-      <c r="C44" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
-        <v>470</v>
-      </c>
-      <c r="B45" s="3">
-        <v>94172</v>
-      </c>
-      <c r="C45" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
-        <v>470</v>
-      </c>
-      <c r="B46" s="3">
-        <v>94173</v>
-      </c>
-      <c r="C46" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
-        <v>470</v>
-      </c>
-      <c r="B47" s="3">
-        <v>94394</v>
-      </c>
-      <c r="C47" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
-        <v>470</v>
-      </c>
-      <c r="B48" s="3">
-        <v>94400</v>
-      </c>
-      <c r="C48" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
-        <v>470</v>
-      </c>
-      <c r="B49" s="3">
-        <v>94404</v>
-      </c>
-      <c r="C49" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
-        <v>470</v>
-      </c>
-      <c r="B50" s="3">
-        <v>95590</v>
-      </c>
-      <c r="C50" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
-        <v>470</v>
-      </c>
-      <c r="B51" s="3">
-        <v>95591</v>
-      </c>
-      <c r="C51" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
-        <v>470</v>
-      </c>
-      <c r="B52" s="3">
-        <v>95735</v>
-      </c>
-      <c r="C52" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
-        <v>470</v>
-      </c>
-      <c r="B53" s="3">
-        <v>95765</v>
-      </c>
-      <c r="C53" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
-        <v>470</v>
-      </c>
-      <c r="B54" s="3">
-        <v>95768</v>
-      </c>
-      <c r="C54" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
-        <v>470</v>
-      </c>
-      <c r="B55" s="3">
-        <v>95781</v>
-      </c>
-      <c r="C55" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
-        <v>470</v>
-      </c>
-      <c r="B56" s="3">
-        <v>95907</v>
-      </c>
-      <c r="C56" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>470</v>
-      </c>
-      <c r="B57" s="3">
-        <v>97116</v>
-      </c>
-      <c r="C57" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
-        <v>470</v>
-      </c>
-      <c r="B58" s="3">
-        <v>97118</v>
-      </c>
-      <c r="C58" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
-        <v>470</v>
-      </c>
-      <c r="B59" s="3">
-        <v>97131</v>
-      </c>
-      <c r="C59" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
-        <v>470</v>
-      </c>
-      <c r="B60" s="3">
-        <v>97245</v>
-      </c>
-      <c r="C60" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
-        <v>470</v>
-      </c>
-      <c r="B61" s="3">
-        <v>97665</v>
-      </c>
-      <c r="C61" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
-        <v>470</v>
-      </c>
-      <c r="B62" s="3">
-        <v>98149</v>
-      </c>
-      <c r="C62" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
-        <v>470</v>
-      </c>
-      <c r="B63" s="3">
-        <v>98151</v>
-      </c>
-      <c r="C63" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
-        <v>470</v>
-      </c>
-      <c r="B64" s="3">
-        <v>98263</v>
-      </c>
-      <c r="C64" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
-        <v>470</v>
-      </c>
-      <c r="B65" s="3">
-        <v>98289</v>
-      </c>
-      <c r="C65" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
-        <v>470</v>
-      </c>
-      <c r="B66" s="3">
-        <v>98344</v>
-      </c>
-      <c r="C66" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
-        <v>470</v>
-      </c>
-      <c r="B67" s="3">
-        <v>98347</v>
-      </c>
-      <c r="C67" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
-        <v>470</v>
-      </c>
-      <c r="B68" s="3">
-        <v>98372</v>
-      </c>
-      <c r="C68" s="3">
         <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
-        <v>470</v>
-      </c>
-      <c r="B69" s="3">
-        <v>98377</v>
-      </c>
-      <c r="C69" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
-        <v>470</v>
-      </c>
-      <c r="B70" s="3">
-        <v>98378</v>
-      </c>
-      <c r="C70" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
-        <v>470</v>
-      </c>
-      <c r="B71" s="3">
-        <v>98437</v>
-      </c>
-      <c r="C71" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
-        <v>470</v>
-      </c>
-      <c r="B72" s="3">
-        <v>98445</v>
-      </c>
-      <c r="C72" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
-        <v>470</v>
-      </c>
-      <c r="B73" s="3">
-        <v>98471</v>
-      </c>
-      <c r="C73" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
-        <v>470</v>
-      </c>
-      <c r="B74" s="3">
-        <v>98540</v>
-      </c>
-      <c r="C74" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
-        <v>470</v>
-      </c>
-      <c r="B75" s="3">
-        <v>98626</v>
-      </c>
-      <c r="C75" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
-        <v>470</v>
-      </c>
-      <c r="B76" s="3">
-        <v>98634</v>
-      </c>
-      <c r="C76" s="3">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
